--- a/มจธ_มศวเกมส์42.xlsx
+++ b/มจธ_มศวเกมส์42.xlsx
@@ -529,17 +529,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 12:00</t>
+          <t>อา. 31/5/2569 9:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>XD35</t>
+          <t>MD35</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 128</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>ดร. สิทถกานต์ สิทธิ / ช่อทิพย์ ระหงษ์</t>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>ทินกร ปงธิยา / กุณฑลี ไชยสี</t>
+          <t>ทินกร ปงธิยา / ทศพล ภูมิดิษฐ์</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
@@ -588,17 +588,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
+          <t>ดร. สิทถกานต์ สิทธิ / ช่อทิพย์ ระหงษ์</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>นพดล พิตพีรฆ / นัยน์ปพร สุภา</t>
+          <t>ทินกร ปงธิยา / กุณฑลี ไชยสี</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>ม.มหามกุฏราชวิทยาลัย</t>
+          <t>ม.เชียงใหม่</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
@@ -607,12 +607,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 12:30</t>
+          <t>อา. 31/5/2569 12:00</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>XDทั่วไป</t>
+          <t>XD35</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -627,17 +627,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
+          <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>กฤติเตมีย์ อ้อนอุบล / พิชาพัชร์ ฐิติธนอภิพงษ์</t>
+          <t>นพดล พิตพีรฆ / นัยน์ปพร สุภา</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>มทร.อีสาน</t>
+          <t>ม.มหามกุฏราชวิทยาลัย</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -646,7 +646,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 14:00</t>
+          <t>อา. 31/5/2569 12:30</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -666,17 +666,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+          <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>อาชวิน เฉลิมชัย / สุพรรณิการ์ ทรัพย์รำลึก</t>
+          <t>กฤติเตมีย์ อ้อนอุบล / พิชาพัชร์ ฐิติธนอภิพงษ์</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ม.เกษตรศาสตร์</t>
+          <t>มทร.อีสาน</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -685,12 +685,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 14:30</t>
+          <t>อา. 31/5/2569 14:00</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>XD40</t>
+          <t>XDทั่วไป</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -705,17 +705,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
+          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>ฐานวัฒน์ พร้อมมูล / พันทิวา ฟองวรรณา</t>
+          <t>อาชวิน เฉลิมชัย / สุพรรณิการ์ ทรัพย์รำลึก</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>อว.</t>
+          <t>ม.เกษตรศาสตร์</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 16:30</t>
+          <t>อา. 31/5/2569 14:30</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -744,17 +744,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>มานะ ภักดีวงศ์ / สุพรรณิกา แก้วน้อย</t>
+          <t>ฐานวัฒน์ พร้อมมูล / พันทิวา ฟองวรรณา</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>ม.เชียงใหม่</t>
+          <t>อว.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
@@ -763,12 +763,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 18:00</t>
+          <t>อา. 31/5/2569 16:30</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>MDทั่วไป</t>
+          <t>XD40</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>ภรัณวัฒน์ ทวีอิสราเมศร์ / เทพปัญญา เหมะธุลินทร์</t>
+          <t>มานะ ภักดีวงศ์ / สุพรรณิกา แก้วน้อย</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>ม.สุโขทัยธรรมาธิราช</t>
+          <t>ม.เชียงใหม่</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
@@ -802,12 +802,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 19:00</t>
+          <t>อา. 31/5/2569 18:00</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>WD40</t>
+          <t>MDทั่วไป</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -822,17 +822,17 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
+          <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>NINETTE MATAAC / ผศ.ดร.สุนทรียา กาละวงศ์</t>
+          <t>ภรัณวัฒน์ ทวีอิสราเมศร์ / เทพปัญญา เหมะธุลินทร์</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>มรภ.บ้านสมเด็จเจ้าพระยา</t>
+          <t>ม.สุโขทัยธรรมาธิราช</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
@@ -841,12 +841,12 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 19:30</t>
+          <t>อา. 31/5/2569 19:00</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>MDทั่วไป</t>
+          <t>WD40</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -861,17 +861,17 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
+          <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>ดร.วันฉัตร ศิริสาร / อาชวิน เฉลิมชัย</t>
+          <t>NINETTE MATAAC / ผศ.ดร.สุนทรียา กาละวงศ์</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>ม.เกษตรศาสตร์</t>
+          <t>มรภ.บ้านสมเด็จเจ้าพระยา</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -880,17 +880,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569 9:30</t>
+          <t>อา. 31/5/2569 19:30</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>MD35</t>
+          <t>MDทั่วไป</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -900,17 +900,17 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
+          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>ทินกร ปงธิยา / ทศพล ภูมิดิษฐ์</t>
+          <t>ดร.วันฉัตร ศิริสาร / อาชวิน เฉลิมชัย</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>ม.เชียงใหม่</t>
+          <t>ม.เกษตรศาสตร์</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
@@ -1937,14 +1937,14 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>XD35
-MD35</t>
+          <t>MD35
+XD35</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>ช่อทิพย์ ระหงษ์
-พิสิษฐ์ วิชานนะ</t>
+          <t>พิสิษฐ์ วิชานนะ
+ช่อทิพย์ ระหงษ์</t>
         </is>
       </c>
     </row>
@@ -2213,14 +2213,14 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>XD35
-MD35</t>
+          <t>MD35
+XD35</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>อรชร กำเนิด
-ดร. สิทถกานต์ สิทธิ</t>
+          <t>ดร. สิทถกานต์ สิทธิ
+อรชร กำเนิด</t>
         </is>
       </c>
     </row>

--- a/มจธ_มศวเกมส์42.xlsx
+++ b/มจธ_มศวเกมส์42.xlsx
@@ -1139,15 +1139,11 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
+          <t>รอคู่แข่ง</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
+      <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1178,15 +1174,11 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
+          <t>รอคู่แข่ง</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
+      <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
@@ -2451,7 +2443,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
@@ -2481,7 +2473,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">

--- a/มจธ_มศวเกมส์42.xlsx
+++ b/มจธ_มศวเกมส์42.xlsx
@@ -919,247 +919,227 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 10:30</t>
+          <t>อา. 31/5/2569</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MD40</t>
+          <t>MDทั่วไป</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
+          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>ณัฐพล สิทธิผล / วุฒิชาติ เกษโกวิท</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ม.สุโขทัยธรรมาธิราช</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr"/>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
       <c r="I12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 11:00</t>
+          <t>อา. 31/5/2569</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MD45</t>
+          <t>MDทั่วไป</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
+          <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>ผศ.ดร.ทศพล รัตน์นิยมชัย / รศ.ดร.สุภกิจ รูปขันธ์</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>ม.เทคโนโลยีสุรนารี</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 11:30</t>
+          <t>อา. 31/5/2569</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>MD45</t>
+          <t>XD40</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr"/>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>นายสุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>ชัยรัตน์ กาญจนพิบูลย์ / รศ.ดร.กมล เอี่ยมพนากิจ</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>ม.ธรรมศาสตร์</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 14:00</t>
+          <t>อา. 31/5/2569</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>MD35</t>
+          <t>XD40</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr"/>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>นิภัทร์ สิงห์สวัสดิ์ / โกศล บรรเทา</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.พระนคร</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 17:00</t>
+          <t>อา. 31/5/2569</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>XD45</t>
+          <t>XDทั่วไป</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
+          <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>พิทักษ์ นวลจันทร์ [1] / ดร.สายรุ้ง บุบผาพันธ์</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
       <c r="I16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 17:30</t>
+          <t>อา. 31/5/2569</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>XD50</t>
+          <t>XDทั่วไป</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
+          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>รอคู่แข่ง</t>
+          <t>Bye</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 18:00</t>
+          <t>จ. 1/6/2569 10:30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>XD45</t>
+          <t>MD40</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1169,32 +1149,36 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>รอคู่แข่ง</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr"/>
+          <t>ณัฐพล สิทธิผล / วุฒิชาติ เกษโกวิท</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>ม.สุโขทัยธรรมาธิราช</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 19:30</t>
+          <t>จ. 1/6/2569 11:00</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>WD45</t>
+          <t>MD45</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1204,17 +1188,17 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>นพนนท์ หาแก้ว / ปาณิสรา ติณธรานนท์</t>
+          <t>ผศ.ดร.ทศพล รัตน์นิยมชัย / รศ.ดร.สุภกิจ รูปขันธ์</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>ม.มหิดล</t>
+          <t>ม.เทคโนโลยีสุรนารี</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
@@ -1223,17 +1207,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 20:00</t>
+          <t>จ. 1/6/2569 11:30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>WD45</t>
+          <t>MD45</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1243,17 +1227,17 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+          <t>นายสุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>ขวัญชนก เฉลิมศรี / แจ่มใส จันทร์กลาง</t>
+          <t>ชัยรัตน์ กาญจนพิบูลย์ / รศ.ดร.กมล เอี่ยมพนากิจ</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>มทร.ล้านนา</t>
+          <t>ม.ธรรมศาสตร์</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -1262,17 +1246,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 13:30</t>
+          <t>จ. 1/6/2569 14:00</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>WD40</t>
+          <t>MD35</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1282,17 +1266,17 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
+          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
+          <t>นิภัทร์ สิงห์สวัสดิ์ / โกศล บรรเทา</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>มรภ.ราชนครินทร์</t>
+          <t>มรภ.พระนคร</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
@@ -1301,12 +1285,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 14:00</t>
+          <t>จ. 1/6/2569 17:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>WD35</t>
+          <t>XD45</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1321,17 +1305,17 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
+          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
+          <t>พิทักษ์ นวลจันทร์ [1] / ดร.สายรุ้ง บุบผาพันธ์</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>ม.ธรรมศาสตร์</t>
+          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -1340,12 +1324,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 14:30</t>
+          <t>จ. 1/6/2569 17:30</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>WD35</t>
+          <t>XD50</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1360,120 +1344,140 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
-        </is>
-      </c>
+          <t>รอคู่แข่ง</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 18:00</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>XD45</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>รอคู่แข่ง</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 19:30</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>นพนนท์ หาแก้ว / ปาณิสรา ติณธรานนท์</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 20:00</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>ขวัญชนก เฉลิมศรี / แจ่มใส จันทร์กลาง</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>มทร.ล้านนา</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>MD35</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>MD40</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr"/>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>MDทั่วไป</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr"/>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>MDทั่วไป</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1484,7 +1488,7 @@
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
+          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1501,21 +1505,25 @@
       <c r="I27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569</t>
+        </is>
+      </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>WD35</t>
+          <t>MD40</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 128</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -1532,10 +1540,14 @@
       <c r="I28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>WD35</t>
+          <t>XD45</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1546,7 +1558,7 @@
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -1563,10 +1575,14 @@
       <c r="I29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569</t>
+        </is>
+      </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>WD40</t>
+          <t>XD45</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1577,7 +1593,7 @@
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
+          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
@@ -1594,21 +1610,25 @@
       <c r="I30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569</t>
+        </is>
+      </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>XD40</t>
+          <t>XD50</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -1625,103 +1645,131 @@
       <c r="I31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 13:30</t>
+        </is>
+      </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>XD40</t>
+          <t>WD40</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr"/>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
+          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
+          <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.ราชนครินทร์</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 14:00</t>
+        </is>
+      </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>XD45</t>
+          <t>WD35</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr"/>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
+          <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>ม.ธรรมศาสตร์</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr"/>
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 14:30</t>
+        </is>
+      </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>XD45</t>
+          <t>WD35</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
+          <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569</t>
+        </is>
+      </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>XD50</t>
+          <t>WD35</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1732,7 +1780,7 @@
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
+          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -1749,21 +1797,25 @@
       <c r="I35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569</t>
+        </is>
+      </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>XDทั่วไป</t>
+          <t>WD35</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
@@ -1780,21 +1832,25 @@
       <c r="I36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569</t>
+        </is>
+      </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>XDทั่วไป</t>
+          <t>WD40</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">

--- a/มจธ_มศวเกมส์42.xlsx
+++ b/มจธ_มศวเกมส์42.xlsx
@@ -44,7 +44,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F47B20"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2F0D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBE5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,10 +93,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -465,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -544,7 +566,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 4</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
@@ -562,47 +584,63 @@
           <t>ม.เชียงใหม่</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>21-11, 19-21, 21-10</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>อา. 31/5/2569 12:00</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>XD35</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Round of 64</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>ดร. สิทถกานต์ สิทธิ / ช่อทิพย์ ระหงษ์</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>ทินกร ปงธิยา / กุณฑลี ไชยสี</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>ม.เชียงใหม่</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>18-21, 16-21</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,7 +660,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 5</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -640,47 +678,63 @@
           <t>ม.มหามกุฏราชวิทยาลัย</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21-11, 21-7</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>อา. 31/5/2569 12:30</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>XDทั่วไป</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Round of 64</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>กฤติเตมีย์ อ้อนอุบล / พิชาพัชร์ ฐิติธนอภิพงษ์</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>มทร.อีสาน</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>21-17, 15-21, 14-21</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -700,7 +754,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 6</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -718,8 +772,16 @@
           <t>ม.เกษตรศาสตร์</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21-15, 17-21, 21-18</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -739,7 +801,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 6</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -757,8 +819,16 @@
           <t>อว.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21-14, 21-18</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -778,7 +848,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 7</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -796,47 +866,63 @@
           <t>ม.เชียงใหม่</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>21-14, 21-15</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>อา. 31/5/2569 18:00</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>MDทั่วไป</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>Round of 64</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>ภรัณวัฒน์ ทวีอิสราเมศร์ / เทพปัญญา เหมะธุลินทร์</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>ม.สุโขทัยธรรมาธิราช</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>16-21, 22-20, 15-21</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -856,7 +942,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 1</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -874,8 +960,16 @@
           <t>มรภ.บ้านสมเด็จเจ้าพระยา</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21-7, 21-8</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -895,7 +989,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 1</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -913,384 +1007,496 @@
           <t>ม.เกษตรศาสตร์</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>18-21, 21-13, 21-14</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569</t>
+          <t>จ. 1/6/2569 10:30</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>MDทั่วไป</t>
+          <t>MD40</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr"/>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 1</t>
+        </is>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
+          <t>ณัฐพล สิทธิผล / วุฒิชาติ เกษโกวิท</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>ม.สุโขทัยธรรมาธิราช</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr"/>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>21-6, 21-7</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569</t>
+          <t>จ. 1/6/2569 11:00</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>MDทั่วไป</t>
+          <t>MD45</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr"/>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 5</t>
+        </is>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr"/>
+          <t>ผศ.ดร.ทศพล รัตน์นิยมชัย / รศ.ดร.สุภกิจ รูปขันธ์</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>ม.เทคโนโลยีสุรนารี</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr"/>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21-11, 21-15</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569</t>
+          <t>จ. 1/6/2569 11:30</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>XD40</t>
+          <t>MD45</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr"/>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr"/>
+          <t>ชัยรัตน์ กาญจนพิบูลย์ / รศ.ดร.กมล เอี่ยมพนากิจ</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>ม.ธรรมศาสตร์</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr"/>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12-21, 21-14, 21-16</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569</t>
+          <t>จ. 1/6/2569 13:00</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>XD40</t>
+          <t>MD35</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr"/>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr"/>
+          <t>จิรา ฉัตรนราธิป / ณรงค์ฤทธิ์ ศรีแก้ว</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr"/>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>22-20, 21-16</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569</t>
+          <t>จ. 1/6/2569 14:00</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>XDทั่วไป</t>
+          <t>MD35</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr"/>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
+          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr"/>
+          <t>นิภัทร์ สิงห์สวัสดิ์ / โกศล บรรเทา</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.พระนคร</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr"/>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21-19, 21-11</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>อา. 31/5/2569</t>
+          <t>จ. 1/6/2569 14:30</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>XDทั่วไป</t>
+          <t>XD40</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
+          <t>รองศาสตราจารย์ ดร.คณิศร์ มาตรา [3/4] / อาจารย์มาริสา เกตุขาว</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>ม.ศรีนครินทรวิโรฒ</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr"/>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-13</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 10:30</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>MD40</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>ณัฐพล สิทธิผล / วุฒิชาติ เกษโกวิท</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>ม.สุโขทัยธรรมาธิราช</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr"/>
-      <c r="I18" s="2" t="inlineStr"/>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 15:30</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 7</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>พงศกร ช้างผึ้ง / ทัชชญา มิ่งสันติสุข</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>ม.บูรพา</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>16-21, 13-21</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 11:00</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>MD45</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร.ทศพล รัตน์นิยมชัย / รศ.ดร.สุภกิจ รูปขันธ์</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>ม.เทคโนโลยีสุรนารี</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr"/>
-      <c r="I19" s="2" t="inlineStr"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 17:00</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>XD45</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 8</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>พิทักษ์ นวลจันทร์ [1] / ดร.สายรุ้ง บุบผาพันธ์</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>10-21, 4-21</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 11:30</t>
+          <t>จ. 1/6/2569 17:00</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>MD45</t>
+          <t>XDทั่วไป</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Round of 64</t>
+          <t>Round of 32</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 1</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>นายสุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
+          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>ชัยรัตน์ กาญจนพิบูลย์ / รศ.ดร.กมล เอี่ยมพนากิจ</t>
+          <t>วรพงศ์ รักษาเดช / สิริวดี ศรีโอสถ</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>ม.ธรรมศาสตร์</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr"/>
-      <c r="I20" s="2" t="inlineStr"/>
+          <t>ม.สงขลานครินทร์</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>21-17, 12-21, 21-15</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 14:00</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>MD35</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>นิภัทร์ สิงห์สวัสดิ์ / โกศล บรรเทา</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.พระนคร</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 17:30</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>XD50</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 8</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร.อภิชาต ดะลุณเพธย์ / ดุจฝัน เอี้ยงสุวรรณปัทมะ</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>ม.เกษตรศาสตร์</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>12-21, 14-21</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 17:00</t>
+          <t>จ. 1/6/2569 18:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>XD45</t>
+          <t>XD35</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1300,36 +1506,44 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 6</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
+          <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>พิทักษ์ นวลจันทร์ [1] / ดร.สายรุ้ง บุบผาพันธ์</t>
+          <t>พิศาล คงเอียด / กุลธิดา เธียรผาติ</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
-      <c r="I22" s="2" t="inlineStr"/>
+          <t>มรภ.กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-12</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 17:30</t>
+          <t>จ. 1/6/2569 18:00</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>XD50</t>
+          <t>XD45</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1339,32 +1553,44 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 2</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
+          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>รอคู่แข่ง</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="2" t="inlineStr"/>
+          <t>ธง บุญเรือง / จิรายุ มีบุศย์</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-8</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 18:00</t>
+          <t>จ. 1/6/2569 19:30</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>XD45</t>
+          <t>WD45</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1374,27 +1600,39 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2</t>
+          <t>อาคารกีฬา2 - 6</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>รอคู่แข่ง</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="2" t="inlineStr"/>
+          <t>นพนนท์ หาแก้ว / ปาณิสรา ติณธรานนท์</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>21-16, 21-19</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 19:30</t>
+          <t>จ. 1/6/2569 20:00</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1409,462 +1647,658 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>อาคารกีฬา2 - 5</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>ขวัญชนก เฉลิมศรี / แจ่มใส จันทร์กลาง</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>มทร.ล้านนา</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 9:00</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>พัฒนชัย กลั่นประโคน / ศิรินันท์ สุรักษ์กิตติกุล</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>23-25, 21-17, 15-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 10:00</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>XDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 7</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร.ภูริทัต กนกกังสดาล / ภิรมณ จำแนกทาน</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>ม.ธรรมศาสตร์</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>5-21, 7-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 11:00</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>XD45</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
           <t>อาคารกีฬา2</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>รศ.ดร.กมล เอี่ยมพนากิจ / สุรางรัตน์ ศิริจำปา</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>ม.ธรรมศาสตร์</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 11:30</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>XD35</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>ทวิช พรหมพิทักษ์กุล / อาจารย์ ดร.ชัญญภัค โตเจริญบดี</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>จุฬาฯ</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
+      <c r="I29" s="6" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 13:30</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>MD45</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>ผู้ช่วยศาสตราจารย์ ดร. พลกฤษณ์ วงษ์สันติสุข [1] / อาจารย์ณัฐวุฒิ สร้อยดอกสน</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>มจพ.</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
+      <c r="I30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 13:30</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>WD40</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>มรภ.ราชนครินทร์</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 14:00</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>WD35</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>ม.ธรรมศาสตร์</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 14:30</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>WD35</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
+      <c r="I33" s="6" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 15:00</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>กฤษดา ประชุมราศี / ปองสันต์ สรรพวานิชกิจ</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>ม.ขอนแก่น</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+      <c r="I34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 15:00</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>WD40</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>อัยย์ญดา สิรินจุลพงศ์ / เพชรรัตน์ มะหะหมัด</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>มรภ.พระนคร</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
+      <c r="I35" s="6" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 15:30</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>ณัฐพันธุ์ กองบัวใหม่ / ดนัย สายสงวนสัตย์</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>ม.แม่ฟ้าหลวง</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+      <c r="I36" s="6" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 16:30</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>MD45</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>นรินทร์ กุลนภาดล / พอเจตน์ ธรรมศิริขวัญ</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="inlineStr">
+        <is>
+          <t>มรภ.ราชนครินทร์</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 18:00</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>MDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>ธนชัย ทะสุใจ / ผศ.วิโรจน์ มงคลเทพ</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>มทร.ล้านนา</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+      <c r="I38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 19:30</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>MD40</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.วีระ ยินดี / วรวุฒิ ตะนุมงคล</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>มทร.ตะวันออก</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+      <c r="I39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>นพนนท์ หาแก้ว / ปาณิสรา ติณธรานนท์</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>ม.มหิดล</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 20:00</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>ดร.รัตน์นที วิโรจน์ฤทธิ์ / ดร.สายรุ้ง บุบผาพันธ์</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
         <is>
           <t>WD45</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>ขวัญชนก เฉลิมศรี / แจ่มใส จันทร์กลาง</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>มทร.ล้านนา</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>MD35</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>MD40</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Round of 128</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr"/>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>XD45</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>XD45</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>XD50</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr"/>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
-        </is>
-      </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 13:30</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>WD40</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.ราชนครินทร์</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 14:00</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>ม.ธรรมศาสตร์</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="2" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 14:30</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr"/>
-      <c r="I34" s="2" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr"/>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>WD40</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="inlineStr">
-        <is>
-          <t>Bye</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>บาย</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>ปิยนันทนา ฤทธิ์เต็ม [2] / พัชรบูรณ์ เนียมสุวรรณ</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>ม.ศรีนครินทรวิโรฒ</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1877,7 +2311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1909,21 +2343,21 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>DR.MANOVA STEPHENRAJ</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>XDทั่วไป
 MDทั่วไป</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>ปัณฑ์ณธร สั้นป้อม
 ธีรภัทร เขษมเวสารัชวุฒิ</t>
@@ -1931,21 +2365,21 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>ช่อทิพย์ ระหงษ์</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>XD35
 WD35</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>ดร. สิทถกานต์ สิทธิ
 วิชชุดา เต๊ะดอเลาะ</t>
@@ -1953,21 +2387,21 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>ดร. ปริยาภัทร นิลสลับ</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>XD40
 WD40</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>วรทัศน์ บุญไข่
 มัทนพรรณ จิ๋วเจียม</t>
@@ -1975,21 +2409,21 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>ดร. สิทถกานต์ สิทธิ</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>MD35
 XD35</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>พิสิษฐ์ วิชานนะ
 ช่อทิพย์ ระหงษ์</t>
@@ -1997,21 +2431,21 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>ดร.สุณิสา สถาพรวจนา</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>XDทั่วไป
 WD45</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>ธีรภัทร เขษมเวสารัชวุฒิ
 ดรุณี พินิจ</t>
@@ -2019,21 +2453,21 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>ดรุณี พินิจ</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>XD50
 WD45</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>ผศ.ดร. พิเชษฐ์ พินิจ
 ดร.สุณิสา สถาพรวจนา</t>
@@ -2041,41 +2475,41 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>ทยากร มหกรเพชร</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>MDทั่วไป</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>ธีรภัทร เขษมเวสารัชวุฒิ</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>XDทั่วไป
 MDทั่วไป</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>ดร.สุณิสา สถาพรวจนา
 DR.MANOVA STEPHENRAJ</t>
@@ -2083,21 +2517,21 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>นิชาพร ยอดมณี</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>XD40
 WD40</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>รศ.ดร. อธิปัตย์ บุญเหมาะ
 อรชร กำเนิด</t>
@@ -2105,341 +2539,323 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>นายสุทธิพงษ์ โสภา</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>MD45</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>ปัณฑ์ณธร สั้นป้อม</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>XDทั่วไป</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>DR.MANOVA STEPHENRAJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>ปรัชญา ภาคแก้ว</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>ผศ.ดร. พิเชษฐ์ พินิจ</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>ปัณฑ์ณธร สั้นป้อม</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>XDทั่วไป</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>DR.MANOVA STEPHENRAJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>ปรัชญา ภาคแก้ว</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>MD35</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. พิเชษฐ์ พินิจ</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>MD45
 XD50</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>นายสุทธิพงษ์ โสภา
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>สุทธิพงษ์ โสภา
 ดรุณี พินิจ</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>MD40
 MD35</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>วรทัศน์ บุญไข่
 ปรัชญา ภาคแก้ว</t>
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>MDทั่วไป</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>ทยากร มหกรเพชร</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>MDทั่วไป</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>ทยากร มหกรเพชร</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>พงศ์พงา จางบัว</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>WD45
 WD35</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>ฤดี วงษ์แก้ว
 ฤดี วงษ์แก้ว</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>พิสิษฐ์ วิชานนะ</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>MD35
 XD35</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>ดร. สิทถกานต์ สิทธิ
 อรชร กำเนิด</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>WD40
 XD45</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>ดร. ปริยาภัทร นิลสลับ
 สัญญา คงทอง</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>รศ.ดร. อธิปัตย์ บุญเหมาะ</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>XD40
 MD45</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>นิชาพร ยอดมณี
 สัญญา คงทอง</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>ฤดี วงษ์แก้ว</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>WD45
 WD35</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>พงศ์พงา จางบัว
 พงศ์พงา จางบัว</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>XD45
 WD35</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>สุทธิพงษ์ โสภา
 ช่อทิพย์ ระหงษ์</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>วรทัศน์ บุญไข่</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>XD40
 MD40</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>ดร. ปริยาภัทร นิลสลับ
 ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>สัญญา คงทอง</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>MD45
 XD45</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>รศ.ดร. อธิปัตย์ บุญเหมาะ
 มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>สุทธิพงษ์ โสภา</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>MD45
+XD45</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ
+วิชชุดา เต๊ะดอเลาะ</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>สุทธิพงษ์ โสภา</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>XD45</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>วิชชุดา เต๊ะดอเลาะ</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>อรชร กำเนิด</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>XD35
 WD40</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>พิสิษฐ์ วิชานนะ
 นิชาพร ยอดมณี</t>
@@ -2465,206 +2881,206 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>สรุปผลงานทีม มจธ.</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr"/>
+      <c r="B1" s="7" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>จำนวนนักกีฬา</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
-        <v>25</v>
+      <c r="B2" s="7" t="n">
+        <v>24</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>จำนวนแมตช์ทั้งหมด</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>36</v>
+      <c r="B3" s="7" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>บาย (ผ่านเข้ารอบ)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>ยังไม่แข่ง/รอผล</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>แพ้</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>ยังไม่แข่ง/รอผล</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>22</v>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr"/>
-      <c r="B8" s="3" t="inlineStr"/>
+      <c r="A8" s="7" t="inlineStr"/>
+      <c r="B8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>ประเภท</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>จำนวนแมตช์</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>MD35</t>
         </is>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>MD40</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>MD45</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>MDทั่วไป</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>MD40</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>WD35</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>MD45</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>MDทั่วไป</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="n">
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>WD40</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="n">
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>XD35</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>WD40</t>
-        </is>
-      </c>
-      <c r="B15" s="3" t="n">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>XD45</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>WD45</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>XD35</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>XD40</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>XD45</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="n">
-        <v>4</v>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>XD50</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>2</v>
+      <c r="B20" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>XDทั่วไป</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="7" t="n">
         <v>4</v>
       </c>
     </row>

--- a/มจธ_มศวเกมส์42.xlsx
+++ b/มจธ_มศวเกมส์42.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1019,415 +1019,343 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>อา. 31/5/2569</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>MDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>อา. 31/5/2569</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>MDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>ทยากร มหกรเพชร / ผศ.ดร. อธิป ดุลย์จินดาชบาพร</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>อา. 31/5/2569</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>อา. 31/5/2569</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>อา. 31/5/2569</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>XDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DR.MANOVA STEPHENRAJ / ปัณฑ์ณธร สั้นป้อม</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>อา. 31/5/2569</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>XDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Round of 128</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Bye</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>บาย</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>จ. 1/6/2569 10:30</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>MD40</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Round of 64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>อาคารกีฬา2 - 1</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
+      <c r="F18" s="3" t="inlineStr">
         <is>
           <t>ณัฐพล สิทธิผล / วุฒิชาติ เกษโกวิท</t>
         </is>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>ม.สุโขทัยธรรมาธิราช</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>ชนะ</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>21-6, 21-7</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>จ. 1/6/2569 11:00</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>MD45</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Round of 64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>อาคารกีฬา2 - 5</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F19" s="3" t="inlineStr">
         <is>
           <t>ผศ.ดร.ทศพล รัตน์นิยมชัย / รศ.ดร.สุภกิจ รูปขันธ์</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>ม.เทคโนโลยีสุรนารี</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>ชนะ</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>21-11, 21-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 11:30</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>MD45</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 3</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>ชัยรัตน์ กาญจนพิบูลย์ / รศ.ดร.กมล เอี่ยมพนากิจ</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>ม.ธรรมศาสตร์</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12-21, 21-14, 21-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 13:00</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>MD35</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 6</t>
-        </is>
-      </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>จิรา ฉัตรนราธิป / ณรงค์ฤทธิ์ ศรีแก้ว</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>ม.มหิดล</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>22-20, 21-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 14:00</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>MD35</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Round of 64</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 3</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
-        </is>
-      </c>
-      <c r="F16" s="3" t="inlineStr">
-        <is>
-          <t>นิภัทร์ สิงห์สวัสดิ์ / โกศล บรรเทา</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.พระนคร</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21-19, 21-11</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 14:30</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>XD40</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 3</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>รองศาสตราจารย์ ดร.คณิศร์ มาตรา [3/4] / อาจารย์มาริสา เกตุขาว</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>ม.ศรีนครินทรวิโรฒ</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21-10, 21-13</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 15:30</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>XD40</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 7</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>พงศกร ช้างผึ้ง / ทัชชญา มิ่งสันติสุข</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>ม.บูรพา</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>แพ้</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="inlineStr">
-        <is>
-          <t>16-21, 13-21</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 17:00</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>XD45</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 8</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>พิทักษ์ นวลจันทร์ [1] / ดร.สายรุ้ง บุบผาพันธ์</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
-        </is>
-      </c>
-      <c r="H19" s="4" t="inlineStr">
-        <is>
-          <t>แพ้</t>
-        </is>
-      </c>
-      <c r="I19" s="4" t="inlineStr">
-        <is>
-          <t>10-21, 4-21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 17:00</t>
+          <t>จ. 1/6/2569 11:30</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>XDทั่วไป</t>
+          <t>MD45</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2 - 1</t>
+          <t>อาคารกีฬา2 - 3</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>วรพงศ์ รักษาเดช / สิริวดี ศรีโอสถ</t>
+          <t>ชัยรัตน์ กาญจนพิบูลย์ / รศ.ดร.กมล เอี่ยมพนากิจ</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>ม.สงขลานครินทร์</t>
+          <t>ม.ธรรมศาสตร์</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1437,91 +1365,91 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21-17, 12-21, 21-15</t>
+          <t>12-21, 21-14, 21-16</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 17:30</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>XD50</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 8</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>ผศ.ดร.อภิชาต ดะลุณเพธย์ / ดุจฝัน เอี้ยงสุวรรณปัทมะ</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>ม.เกษตรศาสตร์</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>แพ้</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>12-21, 14-21</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 13:00</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Round of 64</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>จิรา ฉัตรนราธิป / ณรงค์ฤทธิ์ ศรีแก้ว</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>22-20, 21-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 18:00</t>
+          <t>จ. 1/6/2569 14:00</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>XD35</t>
+          <t>MD35</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Round of 32</t>
+          <t>Round of 64</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>อาคารกีฬา2 - 6</t>
+          <t>อาคารกีฬา2 - 3</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
+          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>พิศาล คงเอียด / กุลธิดา เธียรผาติ</t>
+          <t>นิภัทร์ สิงห์สวัสดิ์ / โกศล บรรเทา</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>มรภ.กาญจนบุรี</t>
+          <t>มรภ.พระนคร</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1531,566 +1459,630 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21-10, 21-12</t>
+          <t>21-19, 21-11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>จ. 1/6/2569 18:00</t>
+          <t>จ. 1/6/2569 14:30</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>รองศาสตราจารย์ ดร.คณิศร์ มาตรา [3/4] / อาจารย์มาริสา เกตุขาว</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>ม.ศรีนครินทรวิโรฒ</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 15:30</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 7</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / นิชาพร ยอดมณี</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>พงศกร ช้างผึ้ง / ทัชชญา มิ่งสันติสุข</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>ม.บูรพา</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>16-21, 13-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 17:00</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>XD45</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 2</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>ธง บุญเรือง / จิรายุ มีบุศย์</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>มรภ.กาญจนบุรี</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 8</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>สุทธิพงษ์ โสภา / วิชชุดา เต๊ะดอเลาะ</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>พิทักษ์ นวลจันทร์ [1] / ดร.สายรุ้ง บุบผาพันธ์</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>10-21, 4-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 17:00</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>XDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 1</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>วรพงศ์ รักษาเดช / สิริวดี ศรีโอสถ</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>ม.สงขลานครินทร์</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>ชนะ</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>21-10, 21-8</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 19:30</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>WD45</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>นพนนท์ หาแก้ว / ปาณิสรา ติณธรานนท์</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>ม.มหิดล</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>21-16, 21-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>จ. 1/6/2569 20:00</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>WD45</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 5</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>ขวัญชนก เฉลิมศรี / แจ่มใส จันทร์กลาง</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>มทร.ล้านนา</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>ชนะ</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>21-10, 21-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 9:00</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>XD40</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Round of 16</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2 - 6</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>พัฒนชัย กลั่นประโคน / ศิรินันท์ สุรักษ์กิตติกุล</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>ม.มหิดล</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr">
-        <is>
-          <t>แพ้</t>
-        </is>
-      </c>
-      <c r="I26" s="4" t="inlineStr">
-        <is>
-          <t>23-25, 21-17, 15-21</t>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>21-17, 12-21, 21-15</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>จ. 1/6/2569 17:30</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>XD50</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 8</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ / ดรุณี พินิจ</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร.อภิชาต ดะลุณเพธย์ / ดุจฝัน เอี้ยงสุวรรณปัทมะ</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>ม.เกษตรศาสตร์</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>12-21, 14-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 18:00</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>XD35</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>พิศาล คงเอียด / กุลธิดา เธียรผาติ</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 18:00</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>XD45</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 2</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>ธง บุญเรือง / จิรายุ มีบุศย์</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.กาญจนบุรี</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 19:30</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>นพนนท์ หาแก้ว / ปาณิสรา ติณธรานนท์</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>21-16, 21-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>จ. 1/6/2569 20:00</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 5</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>ขวัญชนก เฉลิมศรี / แจ่มใส จันทร์กลาง</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>มทร.ล้านนา</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 9:00</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>XD40</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>วรทัศน์ บุญไข่ / ดร. ปริยาภัทร นิลสลับ</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>พัฒนชัย กลั่นประโคน / ศิรินันท์ สุรักษ์กิตติกุล</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>23-25, 21-17, 15-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>อ. 2/6/2569 10:00</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>XDทั่วไป</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>Round of 16</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>อาคารกีฬา2 - 7</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>ธีรภัทร เขษมเวสารัชวุฒิ / ดร.สุณิสา สถาพรวจนา</t>
         </is>
       </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>ผศ.ดร.ภูริทัต กนกกังสดาล / ภิรมณ จำแนกทาน</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>ม.ธรรมศาสตร์</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H33" s="4" t="inlineStr">
         <is>
           <t>แพ้</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I33" s="4" t="inlineStr">
         <is>
           <t>5-21, 7-21</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 11:00</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>XD45</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Round of 16</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 8</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>รศ.ดร.กมล เอี่ยมพนากิจ / สุรางรัตน์ ศิริจำปา</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>ม.ธรรมศาสตร์</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
-      <c r="I28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>21-9, 21-8</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 11:30</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>XD35</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Round of 16</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>พิสิษฐ์ วิชานนะ / อรชร กำเนิด</t>
         </is>
       </c>
-      <c r="F29" s="7" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>ทวิช พรหมพิทักษ์กุล / อาจารย์ ดร.ชัญญภัค โตเจริญบดี</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>จุฬาฯ</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
-      <c r="I29" s="6" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 13:30</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>MD45</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>ผู้ช่วยศาสตราจารย์ ดร. พลกฤษณ์ วงษ์สันติสุข [1] / อาจารย์ณัฐวุฒิ สร้อยดอกสน</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>มจพ.</t>
-        </is>
-      </c>
-      <c r="H30" s="6" t="inlineStr"/>
-      <c r="I30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 13:30</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>WD40</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>มรภ.ราชนครินทร์</t>
-        </is>
-      </c>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 14:00</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
-        </is>
-      </c>
-      <c r="F32" s="7" t="inlineStr">
-        <is>
-          <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
-        </is>
-      </c>
-      <c r="G32" s="7" t="inlineStr">
-        <is>
-          <t>ม.ธรรมศาสตร์</t>
-        </is>
-      </c>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 14:30</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>WD35</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr">
-        <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
-        </is>
-      </c>
-      <c r="G33" s="7" t="inlineStr">
-        <is>
-          <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
-        </is>
-      </c>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 15:00</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>MD35</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
-        <is>
-          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
-        </is>
-      </c>
-      <c r="F34" s="7" t="inlineStr">
-        <is>
-          <t>กฤษดา ประชุมราศี / ปองสันต์ สรรพวานิชกิจ</t>
-        </is>
-      </c>
-      <c r="G34" s="7" t="inlineStr">
-        <is>
-          <t>ม.ขอนแก่น</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="inlineStr"/>
-      <c r="I34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>อ. 2/6/2569 15:00</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>WD40</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>Round of 32</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>อัยย์ญดา สิรินจุลพงศ์ / เพชรรัตน์ มะหะหมัด</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>มรภ.พระนคร</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr"/>
-      <c r="I35" s="6" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>7-21, 5-21</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 15:30</t>
+          <t>อ. 2/6/2569 13:30</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>MD35</t>
+          <t>MD45</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2105,17 +2097,17 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
+          <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ณัฐพันธุ์ กองบัวใหม่ / ดนัย สายสงวนสัตย์</t>
+          <t>ผู้ช่วยศาสตราจารย์ ดร. พลกฤษณ์ วงษ์สันติสุข [1] / อาจารย์ณัฐวุฒิ สร้อยดอกสน</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>ม.แม่ฟ้าหลวง</t>
+          <t>มจพ.</t>
         </is>
       </c>
       <c r="H36" s="6" t="inlineStr"/>
@@ -2124,12 +2116,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 16:30</t>
+          <t>อ. 2/6/2569 13:30</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>MD45</t>
+          <t>WD40</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2144,12 +2136,12 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
+          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>นรินทร์ กุลนภาดล / พอเจตน์ ธรรมศิริขวัญ</t>
+          <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -2163,12 +2155,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 18:00</t>
+          <t>อ. 2/6/2569 14:00</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>MDทั่วไป</t>
+          <t>WD35</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2183,17 +2175,17 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
+          <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>ธนชัย ทะสุใจ / ผศ.วิโรจน์ มงคลเทพ</t>
+          <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>มทร.ล้านนา</t>
+          <t>ม.ธรรมศาสตร์</t>
         </is>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
@@ -2202,12 +2194,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>อ. 2/6/2569 19:30</t>
+          <t>อ. 2/6/2569 14:30</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>MD40</t>
+          <t>WD35</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2222,83 +2214,348 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>ผศ.วีระ ยินดี / วรวุฒิ ตะนุมงคล</t>
+          <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>มทร.ตะวันออก</t>
+          <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
         </is>
       </c>
       <c r="H39" s="6" t="inlineStr"/>
       <c r="I39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr"/>
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 15:00</t>
+        </is>
+      </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>WD45</t>
+          <t>MD35</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>Round of 16</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr"/>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>ดร.รัตน์นที วิโรจน์ฤทธิ์ / ดร.สายรุ้ง บุบผาพันธ์</t>
+          <t>กฤษดา ประชุมราศี / ปองสันต์ สรรพวานิชกิจ</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
+          <t>ม.ขอนแก่น</t>
         </is>
       </c>
       <c r="H40" s="6" t="inlineStr"/>
       <c r="I40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr"/>
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 15:00</t>
+        </is>
+      </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>WD45</t>
+          <t>WD40</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>Round of 16</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr"/>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+          <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>ปิยนันทนา ฤทธิ์เต็ม [2] / พัชรบูรณ์ เนียมสุวรรณ</t>
+          <t>อัยย์ญดา สิรินจุลพงศ์ / เพชรรัตน์ มะหะหมัด</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>ม.ศรีนครินทรวิโรฒ</t>
+          <t>มรภ.พระนคร</t>
         </is>
       </c>
       <c r="H41" s="6" t="inlineStr"/>
       <c r="I41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 15:30</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>ณัฐพันธุ์ กองบัวใหม่ / ดนัย สายสงวนสัตย์</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>ม.แม่ฟ้าหลวง</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+      <c r="I42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 16:30</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>MD45</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>นรินทร์ กุลนภาดล / พอเจตน์ ธรรมศิริขวัญ</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>มรภ.ราชนครินทร์</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
+      <c r="I43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 18:00</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>MDทั่วไป</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>ธนชัย ทะสุใจ / ผศ.วิโรจน์ มงคลเทพ</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>มทร.ล้านนา</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
+      <c r="I44" s="6" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>อ. 2/6/2569 19:30</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>MD40</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>Round of 32</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>ผศ.วีระ ยินดี / วรวุฒิ ตะนุมงคล</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>มทร.ตะวันออก</t>
+        </is>
+      </c>
+      <c r="H45" s="6" t="inlineStr"/>
+      <c r="I45" s="6" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>ดร.รัตน์นที วิโรจน์ฤทธิ์ / ดร.สายรุ้ง บุบผาพันธ์</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
+        </is>
+      </c>
+      <c r="H46" s="6" t="inlineStr"/>
+      <c r="I46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>ปิยนันทนา ฤทธิ์เต็ม [2] / พัชรบูรณ์ เนียมสุวรรณ</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>ม.ศรีนครินทรวิโรฒ</t>
+        </is>
+      </c>
+      <c r="H47" s="6" t="inlineStr"/>
+      <c r="I47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>XD45</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>Quarter final</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>องอาจ เพียงโคกกรวด / ศศิรชา ชัยชมภู</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>ม.เทคโนโลยีสุรนารี</t>
+        </is>
+      </c>
+      <c r="H48" s="6" t="inlineStr"/>
+      <c r="I48" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2905,7 +3162,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -2915,7 +3172,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -2925,7 +3182,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -2935,7 +3192,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -2945,7 +3202,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -3001,7 +3258,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3051,7 +3308,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -3061,7 +3318,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -3081,7 +3338,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/มจธ_มศวเกมส์42.xlsx
+++ b/มจธ_มศวเกมส์42.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ / สุทธิพงษ์ โสภา</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -2075,487 +2075,1038 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 13:30</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>MD45</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>รศ.ดร. อธิปัตย์ บุญเหมาะ / สัญญา คงทอง</t>
         </is>
       </c>
-      <c r="F36" s="7" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>ผู้ช่วยศาสตราจารย์ ดร. พลกฤษณ์ วงษ์สันติสุข [1] / อาจารย์ณัฐวุฒิ สร้อยดอกสน</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="5" t="inlineStr">
         <is>
           <t>มจพ.</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
-      <c r="I36" s="6" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>16-21, 9-21</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 13:30</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>WD40</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 7</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
         <is>
           <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
         </is>
       </c>
-      <c r="F37" s="7" t="inlineStr">
+      <c r="F37" s="3" t="inlineStr">
         <is>
           <t>ภัทรพร คุนาพงษ์กิติ / มธุริน พงศกรพาณิช</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>มรภ.ราชนครินทร์</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
-      <c r="I37" s="6" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>21-2, 21-2</t>
+        </is>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 14:00</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>WD35</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>ช่อทิพย์ ระหงษ์ / วิชชุดา เต๊ะดอเลาะ</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>ฐิตารีย์ ทำทอง / อัมพร มะลิซ้อน</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>ม.ธรรมศาสตร์</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
-      <c r="I38" s="6" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>15-21, 11-21</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 14:30</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>WD35</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 2</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
         <is>
           <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>อาจารย์กุสุมา รวมธรรม / อาจารย์ธิดารัตน์ กันฮะ</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>มรภ.วไลยอลงกรณ์ ในพระบรมราชูปถัมภ์</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr"/>
-      <c r="I39" s="6" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>21-19, 11-21, 23-21</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 15:00</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>MD35</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F40" s="3" t="inlineStr">
         <is>
           <t>กฤษดา ประชุมราศี / ปองสันต์ สรรพวานิชกิจ</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>ม.ขอนแก่น</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr"/>
-      <c r="I40" s="6" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>21-16, 21-8</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 15:00</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>WD40</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 1</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="F41" s="3" t="inlineStr">
         <is>
           <t>อัยย์ญดา สิรินจุลพงศ์ / เพชรรัตน์ มะหะหมัด</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="3" t="inlineStr">
         <is>
           <t>มรภ.พระนคร</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr"/>
-      <c r="I41" s="6" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>21-12, 21-6</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 15:30</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>MD35</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>ปรัชญา ภาคแก้ว / ผศ.ดร. สุธิวัชร ศุภลักษณ์</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>ณัฐพันธุ์ กองบัวใหม่ / ดนัย สายสงวนสัตย์</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="5" t="inlineStr">
         <is>
           <t>ม.แม่ฟ้าหลวง</t>
         </is>
       </c>
-      <c r="H42" s="6" t="inlineStr"/>
-      <c r="I42" s="6" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>19-21, 21-19, 17-21</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 16:30</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>MD45</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="4" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E43" s="7" t="inlineStr">
-        <is>
-          <t>สุทธิพงษ์ โสภา / ผศ.ดร. พิเชษฐ์ พินิจ</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 4</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. พิเชษฐ์ พินิจ / สุทธิพงษ์ โสภา</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>นรินทร์ กุลนภาดล / พอเจตน์ ธรรมศิริขวัญ</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>มรภ.ราชนครินทร์</t>
         </is>
       </c>
-      <c r="H43" s="6" t="inlineStr"/>
-      <c r="I43" s="6" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>21-15, 17-21, 21-23</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 18:00</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>MDทั่วไป</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="4" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 5</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>DR.MANOVA STEPHENRAJ / ธีรภัทร เขษมเวสารัชวุฒิ</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>ธนชัย ทะสุใจ / ผศ.วิโรจน์ มงคลเทพ</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="5" t="inlineStr">
         <is>
           <t>มทร.ล้านนา</t>
         </is>
       </c>
-      <c r="H44" s="6" t="inlineStr"/>
-      <c r="I44" s="6" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>22-20, 23-25, 14-21</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>อ. 2/6/2569 19:30</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>MD40</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>Round of 32</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>อาคารกีฬา2</t>
-        </is>
-      </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>ผศ.วีระ ยินดี / วรวุฒิ ตะนุมงคล</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>มทร.ตะวันออก</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr"/>
-      <c r="I45" s="6" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>21-6, 21-3</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 9:00</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 2</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>นลวัชร์ ขุนลา / วิโรจน์ เชาว์วิเศษ</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.สุราษฎร์ธานี</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>21-10, 21-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 10:00</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>MD40</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 4</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>ชัยยุทธ์ ธนะสมบัติ / มานะ ภักดีวงศ์</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>ม.เชียงใหม่</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>22-20, 21-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 11:30</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>WD35</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 5</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>จารุดา สีสังข์ [3/4] / ไอยย์ศรัย พีรภาพรกุล</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>มรภ.จันทรเกษม</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>14-21, 13-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 12:00</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>WD45</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Round of 16</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 2</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>ดร.สุณิสา สถาพรวจนา / ดรุณี พินิจ</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
+      <c r="F49" s="5" t="inlineStr">
         <is>
           <t>ดร.รัตน์นที วิโรจน์ฤทธิ์ / ดร.สายรุ้ง บุบผาพันธ์</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G49" s="5" t="inlineStr">
         <is>
           <t>ม.มหาจุฬาลงกรณราชวิทยาลัย</t>
         </is>
       </c>
-      <c r="H46" s="6" t="inlineStr"/>
-      <c r="I46" s="6" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr"/>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>11-21, 15-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 13:00</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>WD40</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 7</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>ดร. ปริยาภัทร นิลสลับ / มัทนพรรณ จิ๋วเจียม</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>รศ.ดร.กนิฐพร วังใน / รศ.ดร.ประภาศิริ พงษ์ประยูร</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>ม.เกษตรศาสตร์</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>10-21, 15-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 13:00</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>WD45</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Round of 16</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 8</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
+      <c r="F51" s="3" t="inlineStr">
         <is>
           <t>ปิยนันทนา ฤทธิ์เต็ม [2] / พัชรบูรณ์ เนียมสุวรรณ</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G51" s="3" t="inlineStr">
         <is>
           <t>ม.ศรีนครินทรวิโรฒ</t>
         </is>
       </c>
-      <c r="H47" s="6" t="inlineStr"/>
-      <c r="I47" s="6" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr"/>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>21-11, 21-9</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 13:30</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>WD40</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Round of 16</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>นิชาพร ยอดมณี / อรชร กำเนิด</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>กชพร ชัยสุวรรณ์ [2] / ปาณิสรา ติณธรานนท์</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>10-21, 13-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 15:00</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>XD45</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Quarter final</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 5</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>สัญญา คงทอง / มัทนพรรณ จิ๋วเจียม</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>องอาจ เพียงโคกกรวด / ศศิรชา ชัยชมภู</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>ม.เทคโนโลยีสุรนารี</t>
         </is>
       </c>
-      <c r="H48" s="6" t="inlineStr"/>
-      <c r="I48" s="6" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>21-14, 18-21, 18-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 16:30</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Quarter final</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 3</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>ดร.ณัฐวุฒิ ฉิมมา / ดร.บรรจง เชื้อเมืองพาน</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>มรภ.อุตรดิตถ์</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>ชนะ</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>21-11, 21-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 18:00</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>MD40</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Quarter final</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 4</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>ผศ.ดร. สุธิวัชร ศุภลักษณ์ / วรทัศน์ บุญไข่</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>พัชรศิษฏ์ ปีเจริญ [2] / พัฒนชัย กลั่นประโคน</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>15-21, 16-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>พ. 3/6/2569 18:30</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>WD45</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Quarter final</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 6</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>พงศ์พงา จางบัว / ฤดี วงษ์แก้ว</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>สุกัญญา ทองเย็น / อรวรรณ ห่อหอม</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>ม.มหิดล</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>14-21, 17-21</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>พฤ. 4/6/2569</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>MD35</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Semi final</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>อาคารกีฬา2 - 4</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>ดร. สิทถกานต์ สิทธิ / พิสิษฐ์ วิชานนะ</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>รองศาสตราจารย์ ดร. สุทิน แก่นนาคำ [1] / รองศาสตราจารย์ ดร.จิรัฐติ เต็งสุทธิวัฒน์</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>มจพ.</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>แพ้</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>19-21, 18-21</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3162,7 +3713,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -3182,7 +3733,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -3192,7 +3743,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -3202,7 +3753,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -3228,7 +3779,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -3238,7 +3789,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -3268,7 +3819,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -3278,7 +3829,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -3288,7 +3839,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
